--- a/results/Int Task Remove ACC 1.0/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 1.0/Rando_9_permute.xlsx
@@ -440,87 +440,87 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5364490136148931</v>
+        <v>0.4271950541817171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5340150041678243</v>
+        <v>0.4217407613225896</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5118130036121145</v>
+        <v>0.4255001389274798</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.518638510697416</v>
+        <v>0.498238399555432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5282064462350653</v>
+        <v>0.5095165323701027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5316115587663239</v>
+        <v>0.5218116143373159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.517267296471242</v>
+        <v>0.5153250903028619</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.519609613781606</v>
+        <v>0.5256626840789108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5172214504028897</v>
+        <v>0.5246151708808002</v>
       </c>
     </row>
     <row r="11">
@@ -530,147 +530,147 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5151722700750209</v>
+        <v>0.5246151708808002</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4759780494581828</v>
+        <v>0.5240136148930259</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4756390664073353</v>
+        <v>0.5009474854126146</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4732661850514032</v>
+        <v>0.5480786329535983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4722492358988608</v>
+        <v>0.5648110586273964</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4702000555709919</v>
+        <v>0.5747332592386775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4868866351764379</v>
+        <v>0.5368157821617116</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.478766323978883</v>
+        <v>0.5368157821617116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4688441233676021</v>
+        <v>0.5310072242289525</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4685051403167547</v>
+        <v>0.473275909974993</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4668102250625173</v>
+        <v>0.473275909974993</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4698610725201445</v>
+        <v>0.473275909974993</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4698610725201445</v>
+        <v>0.4899777716032231</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4888594053903862</v>
+        <v>0.4811030841900528</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5035426507363157</v>
+        <v>0.487620172270075</v>
       </c>
     </row>
     <row r="26">
@@ -680,573 +680,573 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.487620172270075</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.5241664351208669</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.5289427618782996</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.5268935815504308</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.5842706307307586</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.4887440955821062</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5032036676854682</v>
+        <v>0.4296262850791887</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5134190052792442</v>
+        <v>0.4456960266740761</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5089816615726591</v>
+        <v>0.4242484023339816</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5089816615726591</v>
+        <v>0.463628785773826</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5113239788830231</v>
+        <v>0.5397874409558211</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5116935259794387</v>
+        <v>0.4973256460127813</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5113545429285913</v>
+        <v>0.5119630452903584</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5113545429285913</v>
+        <v>0.5273701028063351</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5113545429285913</v>
+        <v>0.5700639066407335</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5075951653237011</v>
+        <v>0.5772283967768825</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4855459849958322</v>
+        <v>0.5295415393164769</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4960850236176716</v>
+        <v>0.5801569880522367</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4957460405668241</v>
+        <v>0.561714365101417</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.500137538205057</v>
+        <v>0.566829674909697</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4868713531536538</v>
+        <v>0.5167088080022229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5072409002500694</v>
+        <v>0.440150041678244</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.50414420672409</v>
+        <v>0.4394442900805779</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5024340094470686</v>
+        <v>0.4434051125312586</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5007085301472631</v>
+        <v>0.4434051125312586</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4996915809947208</v>
+        <v>0.4423881633787163</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4989983328702417</v>
+        <v>0.4928813559322034</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4986746318421784</v>
+        <v>0.4928813559322034</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4973339816615726</v>
+        <v>0.4928813559322034</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4953000833564879</v>
+        <v>0.4959322033898305</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4919408168935815</v>
+        <v>0.4959322033898305</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4919408168935815</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4906001667129758</v>
+        <v>0.4972881355932203</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4912781328146708</v>
+        <v>0.4871186440677966</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.493651014170603</v>
+        <v>0.4972881355932203</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.489244234509586</v>
+        <v>0.4972881355932203</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4834051125312587</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4922186718532925</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4925423728813559</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4888135593220339</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.491864406779661</v>
+        <v>0.5024034454015004</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4942372881355932</v>
+        <v>0.5184426229508197</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4925423728813559</v>
+        <v>0.5184426229508197</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4972881355932203</v>
+        <v>0.5184426229508197</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4972881355932203</v>
+        <v>0.5140052792442346</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4989830508474576</v>
+        <v>0.5017101972770214</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4989830508474576</v>
+        <v>0.5089052514587386</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4979661016949152</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4983050847457627</v>
+        <v>0.4996610169491525</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5037593776048902</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4989830508474576</v>
+        <v>0.5136662961933871</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5116171158655182</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5092289524868019</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4989830508474576</v>
+        <v>0.5157154765212559</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5157154765212559</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.5095679355376493</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1256,7 +1256,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1266,7 +1266,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,7 +1286,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,21 +1306,21 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4989830508474576</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
